--- a/casus hackaton.xlsx
+++ b/casus hackaton.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AVJBASTE\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pascal/projects/quintor/svb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:101_{5E7E7BD8-77DE-40B8-AA61-8C882DAFA269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9339D68B-8019-8F4C-BF6F-A714898C7750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1464" yWindow="2532" windowWidth="17280" windowHeight="8880" xr2:uid="{80954343-1134-47C3-8762-FA936ED9CB61}"/>
+    <workbookView xWindow="0" yWindow="800" windowWidth="36000" windowHeight="22580" xr2:uid="{80954343-1134-47C3-8762-FA936ED9CB61}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="86">
   <si>
     <t>de beoordelingsdatum</t>
   </si>
@@ -101,9 +101,6 @@
     <t>de soort verplichting die de persoon heeft overtreden</t>
   </si>
   <si>
-    <t>nakomen verplichting tweede categorie</t>
-  </si>
-  <si>
     <t>gedurende de afgelopen twee jaar voor de huidige overtreding is er minimaal één maatregel o.g.v. dezelfde wet bekendgemaakt vanwege het niet tijdig reageren op een informatieverzoek</t>
   </si>
   <si>
@@ -210,13 +207,103 @@
   </si>
   <si>
     <t>kind2</t>
+  </si>
+  <si>
+    <t>normaalLevenspatroonPersoon</t>
+  </si>
+  <si>
+    <t>Variabele test object</t>
+  </si>
+  <si>
+    <t>emotioneleOntwrichting</t>
+  </si>
+  <si>
+    <t>svbWasTijdigOpDeHoogte</t>
+  </si>
+  <si>
+    <t>buitengewoneOmstandigheid</t>
+  </si>
+  <si>
+    <t>administratiefOnbekwaam</t>
+  </si>
+  <si>
+    <t>heeftOnjuisteInlichtingenTijdigHersteld</t>
+  </si>
+  <si>
+    <t>heeftInlichtingenVerstrektBijSvbControle</t>
+  </si>
+  <si>
+    <t>soortOvertredenVerplichting</t>
+  </si>
+  <si>
+    <t>heeftRecidiveNietTijdigReagerenBinnenTweeJaar</t>
+  </si>
+  <si>
+    <t>heeftRecidiveNietReagerenBinnenTweeJaar</t>
+  </si>
+  <si>
+    <t>heeftMaatregelwaarschuwingBinnenTweeJaar</t>
+  </si>
+  <si>
+    <t>schorsingsbeslissingGenomen</t>
+  </si>
+  <si>
+    <t>isOvertredingGedeeltelijkVerwijtbaar</t>
+  </si>
+  <si>
+    <t>isOvertredingMedeTeWijtenAanSvb</t>
+  </si>
+  <si>
+    <t>isMeldplichtigeVerhuizingBuitenland</t>
+  </si>
+  <si>
+    <t>heeftSvbInhoudingenZvwOfWlzOpgevraagd</t>
+  </si>
+  <si>
+    <t>heeftSvbInformatieGevraagdBijBezwaar</t>
+  </si>
+  <si>
+    <t>isBetalingGestaaktOpVerzoek</t>
+  </si>
+  <si>
+    <t>overtredenAkwVerplichting</t>
+  </si>
+  <si>
+    <t>isMedewerkingsplichtigAkw</t>
+  </si>
+  <si>
+    <t>isInstelling</t>
+  </si>
+  <si>
+    <t>isInhoudingsuitkeringBeeindigd</t>
+  </si>
+  <si>
+    <t>heeftSvbBoetewaarschuwingVoorZelfdeGedraging</t>
+  </si>
+  <si>
+    <t>heeftSvbBoeteVoorZelfdeGedraging</t>
+  </si>
+  <si>
+    <t>isDringendeRedenAanwezig</t>
+  </si>
+  <si>
+    <t>heeftOvertredingBenadelingsbedrag</t>
+  </si>
+  <si>
+    <t>geboortedatumKind1</t>
+  </si>
+  <si>
+    <t>geboortedatumKind2</t>
+  </si>
+  <si>
+    <t>beleidsvoorbeeldEmotioneleOntwrichting</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -230,6 +317,12 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -277,7 +370,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -302,9 +395,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -320,7 +414,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Kantoorthema">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -636,50 +730,52 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B301B29-CF91-4A5C-89D9-2D598FBE3789}">
-  <dimension ref="A1:E151"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F150"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.77734375" customWidth="1"/>
-    <col min="2" max="2" width="81.33203125" customWidth="1"/>
-    <col min="3" max="3" width="46.88671875" customWidth="1"/>
-    <col min="4" max="4" width="36.33203125" customWidth="1"/>
-    <col min="5" max="5" width="49.109375" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="38.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="81.33203125" customWidth="1"/>
+    <col min="4" max="4" width="46.83203125" customWidth="1"/>
+    <col min="5" max="5" width="36.33203125" customWidth="1"/>
+    <col min="6" max="6" width="49.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="6"/>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B2" s="8"/>
-      <c r="C2" s="3"/>
-      <c r="E2" s="3"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" s="11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C2" s="8"/>
+      <c r="D2" s="3"/>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="3"/>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="3"/>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="C4" s="8" t="s">
         <v>0</v>
-      </c>
-      <c r="C4" s="4">
-        <v>46287</v>
       </c>
       <c r="D4" s="4">
         <v>46287</v>
@@ -687,13 +783,16 @@
       <c r="E4" s="4">
         <v>46287</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="8" t="s">
+      <c r="F4" s="4">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>4</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>15</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>15</v>
@@ -701,123 +800,141 @@
       <c r="E5" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="8" t="s">
+      <c r="F5" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="C6" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="8" t="s">
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="C7" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="8" t="s">
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="C8" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-    </row>
-    <row r="9" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B9" s="8" t="s">
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:6" ht="48" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="D9" s="3" t="s">
         <v>5</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="8" t="s">
+      <c r="F9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="D10" s="3" t="s">
         <v>5</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B11" s="8" t="s">
+      <c r="F10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="D12" s="3" t="s">
         <v>5</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="8" t="s">
+      <c r="F12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="C13" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="8" t="s">
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="8" t="s">
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="C15" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
-    </row>
-    <row r="16" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B16" s="8" t="s">
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>14</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>15</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>15</v>
@@ -825,29 +942,32 @@
       <c r="E16" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B17" s="8" t="s">
+      <c r="F16" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="C17" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
-    </row>
-    <row r="18" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B18" s="8" t="s">
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" spans="2:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="C18" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B19" s="8" t="s">
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" spans="2:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>16</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>15</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>15</v>
@@ -855,710 +975,864 @@
       <c r="E19" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="8" t="s">
+      <c r="F19" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="5"/>
-      <c r="E20" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B21" s="8" t="s">
+      <c r="D20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="5"/>
+      <c r="F20" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B22" s="8" t="s">
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" ht="31" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" ht="30.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="8" t="s">
+      <c r="D23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" ht="31.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C24" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" ht="31.35" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
-    </row>
-    <row r="25" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B25" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C25" s="3"/>
+      <c r="F24" s="3"/>
+    </row>
+    <row r="25" spans="2:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="C25" s="8" t="s">
+        <v>24</v>
+      </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B26" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>20</v>
+      <c r="F25" s="3"/>
+    </row>
+    <row r="26" spans="2:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B27" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="5"/>
+      <c r="F26" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="B28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B29" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="C30" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+    </row>
+    <row r="31" spans="2:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B31" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B32" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E33" s="5"/>
+      <c r="F33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="48" x14ac:dyDescent="0.2">
+      <c r="B34" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B35" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B37" t="s">
+        <v>78</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="C38" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+    </row>
+    <row r="39" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A39" s="2"/>
+      <c r="B39" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B40" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B41" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B42" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C42" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="D42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D43" s="3"/>
+      <c r="F43" s="3"/>
+    </row>
+    <row r="44" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="C44" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D44" s="3"/>
+      <c r="F44" s="3"/>
+    </row>
+    <row r="45" spans="1:6" ht="48" x14ac:dyDescent="0.2">
+      <c r="C45" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D46" s="3"/>
+      <c r="F46" s="3"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B47" s="2"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="3"/>
+      <c r="F47" s="3"/>
+    </row>
+    <row r="48" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>39</v>
+      </c>
+      <c r="B48" t="s">
+        <v>83</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D48" s="4">
+        <v>42454</v>
+      </c>
+      <c r="E48" s="4">
+        <v>42454</v>
+      </c>
+      <c r="F48" s="4">
+        <v>42454</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>39</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D27" s="5"/>
-      <c r="E27" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B28" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B29" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B30" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B31" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-    </row>
-    <row r="32" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B32" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B33" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B34" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D34" s="5"/>
-      <c r="E34" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B35" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B36" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B37" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B38" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B39" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="2"/>
-      <c r="B40" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B41" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B42" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B43" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C44" s="3"/>
-      <c r="E44" s="3"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B45" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C45" s="3"/>
-      <c r="E45" s="3"/>
-    </row>
-    <row r="46" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B46" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C47" s="3"/>
-      <c r="E47" s="3"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B48" s="9"/>
-      <c r="C48" s="3"/>
-      <c r="E48" s="3"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>40</v>
-      </c>
-      <c r="B49" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C49" s="4">
-        <v>42454</v>
-      </c>
-      <c r="D49" s="4">
-        <v>42454</v>
-      </c>
-      <c r="E49" s="4">
-        <v>42454</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="8" t="s">
+    </row>
+    <row r="50" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A50" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B50" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D50" s="4">
+        <v>43191</v>
+      </c>
+      <c r="E50" s="1">
+        <v>43191</v>
+      </c>
+      <c r="F50" s="4">
+        <v>43191</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B51" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C51" s="4">
-        <v>43191</v>
-      </c>
-      <c r="D51" s="1">
-        <v>43191</v>
-      </c>
-      <c r="E51" s="4">
-        <v>43191</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B52" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C52" s="3"/>
-      <c r="E52" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B51" s="3"/>
+      <c r="C51" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D51" s="3"/>
+      <c r="F51" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A52" s="3"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="3"/>
+      <c r="F52" s="3"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="3"/>
-      <c r="B53" s="10"/>
-      <c r="C53" s="3"/>
-      <c r="E53" s="3"/>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B53" s="3"/>
+      <c r="C53" s="8"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="3"/>
-      <c r="B54" s="8"/>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B54" s="3"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" s="3"/>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B55" s="3"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" s="3"/>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B56" s="3"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="3"/>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B57" s="3"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="3"/>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B58" s="3"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="3"/>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B59" s="3"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="3"/>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B60" s="3"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="3"/>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B61" s="3"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="3"/>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B62" s="3"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="3"/>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B63" s="3"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" s="3"/>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B64" s="3"/>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" s="3"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B65" s="3"/>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" s="3"/>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B66" s="3"/>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" s="3"/>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B67" s="3"/>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" s="3"/>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B68" s="3"/>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" s="3"/>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B69" s="3"/>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" s="3"/>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B70" s="3"/>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" s="3"/>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B71" s="3"/>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" s="3"/>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B72" s="3"/>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" s="3"/>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B73" s="3"/>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" s="3"/>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B74" s="3"/>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" s="3"/>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B75" s="3"/>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" s="3"/>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B76" s="3"/>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" s="3"/>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B77" s="3"/>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" s="3"/>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B78" s="3"/>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" s="3"/>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B79" s="3"/>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80" s="3"/>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B80" s="3"/>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" s="3"/>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B81" s="3"/>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" s="3"/>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B82" s="3"/>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" s="3"/>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B83" s="3"/>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" s="3"/>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B84" s="3"/>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" s="3"/>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B85" s="3"/>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" s="3"/>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B86" s="3"/>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" s="3"/>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B87" s="3"/>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" s="3"/>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B88" s="3"/>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" s="3"/>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B89" s="3"/>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" s="3"/>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B90" s="3"/>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A91" s="3"/>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B91" s="3"/>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" s="3"/>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B92" s="3"/>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" s="3"/>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B93" s="3"/>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" s="3"/>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B94" s="3"/>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A95" s="3"/>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B95" s="3"/>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" s="3"/>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B96" s="3"/>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" s="3"/>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B97" s="3"/>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98" s="3"/>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B98" s="3"/>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99" s="3"/>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B99" s="3"/>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" s="3"/>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B100" s="3"/>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101" s="3"/>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B101" s="3"/>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A102" s="3"/>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B102" s="3"/>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A103" s="3"/>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B103" s="3"/>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A104" s="3"/>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B104" s="3"/>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A105" s="3"/>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B105" s="3"/>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" s="3"/>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B106" s="3"/>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A107" s="3"/>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B107" s="3"/>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A108" s="3"/>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B108" s="3"/>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A109" s="3"/>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B109" s="3"/>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A110" s="3"/>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B110" s="3"/>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A111" s="3"/>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B111" s="3"/>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A112" s="3"/>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B112" s="3"/>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" s="3"/>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B113" s="3"/>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A114" s="3"/>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B114" s="3"/>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A115" s="3"/>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B115" s="3"/>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A116" s="3"/>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B116" s="3"/>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A117" s="3"/>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B117" s="3"/>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A118" s="3"/>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B118" s="3"/>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A119" s="3"/>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B119" s="3"/>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A120" s="3"/>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B120" s="3"/>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" s="3"/>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B121" s="3"/>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A122" s="3"/>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B122" s="3"/>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A123" s="3"/>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B123" s="3"/>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A124" s="3"/>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B124" s="3"/>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A125" s="3"/>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B125" s="3"/>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A126" s="3"/>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B126" s="3"/>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A127" s="3"/>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B127" s="3"/>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A128" s="3"/>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B128" s="3"/>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A129" s="3"/>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B129" s="3"/>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A130" s="3"/>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B130" s="3"/>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A131" s="3"/>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B131" s="3"/>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A132" s="3"/>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B132" s="3"/>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A133" s="3"/>
-    </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B133" s="3"/>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A134" s="3"/>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B134" s="3"/>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A135" s="3"/>
-    </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B135" s="3"/>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A136" s="3"/>
-    </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B136" s="3"/>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A137" s="3"/>
-    </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B137" s="3"/>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A138" s="3"/>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B138" s="3"/>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A139" s="3"/>
-    </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B139" s="3"/>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A140" s="3"/>
-    </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B140" s="3"/>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A141" s="3"/>
-    </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B141" s="3"/>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A142" s="3"/>
-    </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B142" s="3"/>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" s="3"/>
-    </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B143" s="3"/>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A144" s="3"/>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B144" s="3"/>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A145" s="3"/>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B145" s="3"/>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" s="3"/>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B146" s="3"/>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A147" s="3"/>
-    </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B147" s="3"/>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" s="3"/>
-    </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B148" s="3"/>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A149" s="3"/>
-    </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B149" s="3"/>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A150" s="3"/>
-    </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A151" s="3"/>
+      <c r="B150" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 

--- a/casus hackaton.xlsx
+++ b/casus hackaton.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pascal/projects/quintor/svb/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Code\svb-hackathon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9339D68B-8019-8F4C-BF6F-A714898C7750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5694AAD-2D75-46F7-B0AD-A82C35FF726E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="800" windowWidth="36000" windowHeight="22580" xr2:uid="{80954343-1134-47C3-8762-FA936ED9CB61}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{80954343-1134-47C3-8762-FA936ED9CB61}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="87">
   <si>
     <t>de beoordelingsdatum</t>
   </si>
@@ -297,6 +297,9 @@
   </si>
   <si>
     <t>beleidsvoorbeeldEmotioneleOntwrichting</t>
+  </si>
+  <si>
+    <t>verhuizingTijdigGemeldNaVerzoek</t>
   </si>
 </sst>
 </file>
@@ -731,17 +734,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B301B29-CF91-4A5C-89D9-2D598FBE3789}">
   <dimension ref="A1:F150"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="38.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.77734375" customWidth="1"/>
+    <col min="2" max="2" width="38.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="81.33203125" customWidth="1"/>
-    <col min="4" max="4" width="46.83203125" customWidth="1"/>
+    <col min="4" max="4" width="46.77734375" customWidth="1"/>
     <col min="5" max="5" width="36.33203125" customWidth="1"/>
-    <col min="6" max="6" width="49.1640625" customWidth="1"/>
+    <col min="6" max="6" width="49.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6" t="s">
         <v>57</v>
@@ -759,12 +762,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C2" s="8"/>
       <c r="D2" s="3"/>
       <c r="F2" s="3"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>40</v>
       </c>
@@ -773,7 +776,7 @@
       <c r="D3" s="3"/>
       <c r="F3" s="3"/>
     </row>
-    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C4" s="8" t="s">
         <v>0</v>
       </c>
@@ -787,7 +790,7 @@
         <v>46287</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>56</v>
       </c>
@@ -804,7 +807,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C6" s="8" t="s">
         <v>6</v>
       </c>
@@ -812,7 +815,7 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C7" s="8" t="s">
         <v>7</v>
       </c>
@@ -820,7 +823,7 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C8" s="8" t="s">
         <v>8</v>
       </c>
@@ -828,7 +831,7 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="1:6" ht="48" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>59</v>
       </c>
@@ -845,7 +848,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>58</v>
       </c>
@@ -862,7 +865,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>85</v>
       </c>
@@ -879,7 +882,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>60</v>
       </c>
@@ -896,7 +899,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C13" s="8" t="s">
         <v>11</v>
       </c>
@@ -904,7 +907,7 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
     </row>
-    <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>61</v>
       </c>
@@ -921,7 +924,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C15" s="8" t="s">
         <v>12</v>
       </c>
@@ -929,7 +932,7 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
     </row>
-    <row r="16" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>62</v>
       </c>
@@ -946,7 +949,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="2:6" ht="32" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C17" s="8" t="s">
         <v>17</v>
       </c>
@@ -954,7 +957,7 @@
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
     </row>
-    <row r="18" spans="2:6" ht="32" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C18" s="8" t="s">
         <v>18</v>
       </c>
@@ -962,7 +965,7 @@
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
     </row>
-    <row r="19" spans="2:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>63</v>
       </c>
@@ -979,7 +982,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="2:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>64</v>
       </c>
@@ -994,7 +997,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="2:6" ht="32" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>65</v>
       </c>
@@ -1011,7 +1014,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="2:6" ht="32" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>66</v>
       </c>
@@ -1028,7 +1031,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="2:6" ht="31" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:6" ht="31.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>67</v>
       </c>
@@ -1045,7 +1048,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="2:6" ht="31.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:6" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C24" s="8" t="s">
         <v>23</v>
       </c>
@@ -1053,7 +1056,7 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
     </row>
-    <row r="25" spans="2:6" ht="32" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C25" s="8" t="s">
         <v>24</v>
       </c>
@@ -1061,7 +1064,7 @@
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
     </row>
-    <row r="26" spans="2:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>68</v>
       </c>
@@ -1076,7 +1079,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="2:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>69</v>
       </c>
@@ -1093,7 +1096,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="2:6" ht="32" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>70</v>
       </c>
@@ -1110,7 +1113,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="2:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>71</v>
       </c>
@@ -1127,7 +1130,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="2:6" ht="32" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>86</v>
+      </c>
       <c r="C30" s="8" t="s">
         <v>31</v>
       </c>
@@ -1135,7 +1141,7 @@
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
     </row>
-    <row r="31" spans="2:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>72</v>
       </c>
@@ -1152,7 +1158,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="2:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>73</v>
       </c>
@@ -1169,7 +1175,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>74</v>
       </c>
@@ -1184,7 +1190,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="48" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>75</v>
       </c>
@@ -1201,7 +1207,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>76</v>
       </c>
@@ -1218,7 +1224,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>77</v>
       </c>
@@ -1235,7 +1241,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>78</v>
       </c>
@@ -1252,7 +1258,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C38" s="8" t="s">
         <v>43</v>
       </c>
@@ -1260,7 +1266,7 @@
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
     </row>
-    <row r="39" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="2"/>
       <c r="B39" s="12" t="s">
         <v>79</v>
@@ -1278,7 +1284,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B40" s="12" t="s">
         <v>80</v>
       </c>
@@ -1295,7 +1301,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B41" s="12" t="s">
         <v>81</v>
       </c>
@@ -1312,7 +1318,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B42" s="12" t="s">
         <v>82</v>
       </c>
@@ -1329,18 +1335,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D43" s="3"/>
       <c r="F43" s="3"/>
     </row>
-    <row r="44" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C44" s="9" t="s">
         <v>52</v>
       </c>
       <c r="D44" s="3"/>
       <c r="F44" s="3"/>
     </row>
-    <row r="45" spans="1:6" ht="48" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C45" s="8" t="s">
         <v>51</v>
       </c>
@@ -1351,11 +1357,11 @@
         <v>50</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D46" s="3"/>
       <c r="F46" s="3"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>38</v>
       </c>
@@ -1364,7 +1370,7 @@
       <c r="D47" s="3"/>
       <c r="F47" s="3"/>
     </row>
-    <row r="48" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>39</v>
       </c>
@@ -1384,7 +1390,7 @@
         <v>42454</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>39</v>
       </c>
@@ -1397,7 +1403,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>55</v>
       </c>
@@ -1417,7 +1423,7 @@
         <v>43191</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>55</v>
       </c>
@@ -1430,403 +1436,403 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="10"/>
       <c r="D52" s="3"/>
       <c r="F52" s="3"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="8"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
     </row>

--- a/casus hackaton.xlsx
+++ b/casus hackaton.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Code\svb-hackathon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5694AAD-2D75-46F7-B0AD-A82C35FF726E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B199DA79-7990-4A8A-B73F-7B05FC0A3488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{80954343-1134-47C3-8762-FA936ED9CB61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="88">
   <si>
     <t>de beoordelingsdatum</t>
   </si>
@@ -300,6 +300,9 @@
   </si>
   <si>
     <t>verhuizingTijdigGemeldNaVerzoek</t>
+  </si>
+  <si>
+    <t>uitkeringKanHerleven</t>
   </si>
 </sst>
 </file>
@@ -1259,6 +1262,9 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
+        <v>87</v>
+      </c>
       <c r="C38" s="8" t="s">
         <v>43</v>
       </c>

--- a/casus hackaton.xlsx
+++ b/casus hackaton.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Code\svb-hackathon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B199DA79-7990-4A8A-B73F-7B05FC0A3488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCAF9C9D-3CBE-4C51-A242-D85D654BE9AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{80954343-1134-47C3-8762-FA936ED9CB61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="90">
   <si>
     <t>de beoordelingsdatum</t>
   </si>
@@ -303,6 +303,12 @@
   </si>
   <si>
     <t>uitkeringKanHerleven</t>
+  </si>
+  <si>
+    <t>voorzieneOmstandigheid</t>
+  </si>
+  <si>
+    <t>gewensteOmstandigheid</t>
   </si>
 </sst>
 </file>
@@ -811,6 +817,9 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>89</v>
+      </c>
       <c r="C6" s="8" t="s">
         <v>6</v>
       </c>
@@ -819,6 +828,9 @@
       <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>88</v>
+      </c>
       <c r="C7" s="8" t="s">
         <v>7</v>
       </c>

--- a/casus hackaton.xlsx
+++ b/casus hackaton.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Code\svb-hackathon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCAF9C9D-3CBE-4C51-A242-D85D654BE9AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA1BCAE-82EE-4380-BD12-127B5245AD1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{80954343-1134-47C3-8762-FA936ED9CB61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="91">
   <si>
     <t>de beoordelingsdatum</t>
   </si>
@@ -309,6 +309,9 @@
   </si>
   <si>
     <t>gewensteOmstandigheid</t>
+  </si>
+  <si>
+    <t>nakomenFeitelijkOnmogelijk</t>
   </si>
 </sst>
 </file>
@@ -839,6 +842,9 @@
       <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>90</v>
+      </c>
       <c r="C8" s="8" t="s">
         <v>8</v>
       </c>
